--- a/data/trans_bre/P6907S1-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6907S1-Clase-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 14,97</t>
+          <t>-10,73; 15,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,77</t>
+          <t>0,0; 32,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 6,28</t>
+          <t>-9,08; 4,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 14,8</t>
+          <t>-7,1; 14,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,57; 220,57</t>
+          <t>-66,92; 266,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,69; 557,05</t>
+          <t>-55,59; 665,0</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 7,0</t>
+          <t>-27,53; 7,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 59,61</t>
+          <t>-9,53; 59,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 0,0</t>
+          <t>-18,03; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 22,82</t>
+          <t>-7,0; 23,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>-90,26; 127,07</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 509,93</t>
+          <t>-64,56; 745,88</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 19,63</t>
+          <t>-12,0; 19,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,57; -2,86</t>
+          <t>-24,17; -2,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,07; -3,21</t>
+          <t>-16,87; -3,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 6,44</t>
+          <t>-29,67; 7,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 571,08</t>
+          <t>-100,0; 469,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-90,5; 85,02</t>
+          <t>-91,9; 81,81</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 19,61</t>
+          <t>0,15; 21,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -1,81</t>
+          <t>-16,61; -1,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 6,05</t>
+          <t>-2,07; 5,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 6,74</t>
+          <t>-6,48; 7,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 484,97</t>
+          <t>-2,94; 573,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,62; 143,72</t>
+          <t>-62,65; 178,53</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 8,19</t>
+          <t>-13,15; 7,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 13,73</t>
+          <t>-4,37; 13,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 1,65</t>
+          <t>-15,72; 1,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-82,35; 228,9</t>
+          <t>-82,21; 193,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1095,14 +1095,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-92,94; 101,12</t>
+          <t>-92,75; 68,11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,65</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-48,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-29,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-28,08%</t>
         </is>
       </c>
     </row>
@@ -1160,160 +1160,59 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,18; 6,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,54; 2,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,84; 2,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,96; 1,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-29,84; 92,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 124,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,6; 119,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-57,95; 20,11</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-2,65</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,04</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-48,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-29,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-28,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,84; 6,84</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-7,91; 2,17</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-3,54; 2,08</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-7,7; 1,6</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-26,04; 88,33</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 96,97</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-79,45; 108,62</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-56,71; 21,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>

--- a/data/trans_bre/P6907S1-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6907S1-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 15,17</t>
+          <t>-9,97; 14,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,97</t>
+          <t>0,0; 33,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 4,52</t>
+          <t>-7,58; 4,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 14,77</t>
+          <t>-13,54; 13,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,92; 266,01</t>
+          <t>-63,14; 240,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 665,0</t>
+          <t>-68,23; 381,63</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 7,29</t>
+          <t>-25,44; 6,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 59,01</t>
+          <t>-9,58; 59,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 0,0</t>
+          <t>-18,38; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 23,34</t>
+          <t>-6,95; 21,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-90,26; 127,07</t>
+          <t>-89,8; 128,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,56; 745,88</t>
+          <t>-59,97; 446,07</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-12,37</t>
+          <t>-13,49</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-51,67%</t>
+          <t>-57,16%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 19,3</t>
+          <t>-12,64; 14,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,17; -2,86</t>
+          <t>-23,7; -2,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,87; -3,12</t>
+          <t>-16,61; -3,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 7,3</t>
+          <t>-30,99; 2,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 469,36</t>
+          <t>-100,0; 564,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-91,9; 81,81</t>
+          <t>-96,52; 41,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-1,89%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 21,65</t>
+          <t>-1,15; 19,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,61; -1,92</t>
+          <t>-16,03; -1,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 5,86</t>
+          <t>-2,01; 5,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 7,33</t>
+          <t>-5,07; 7,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 573,02</t>
+          <t>-24,93; 499,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,65; 178,53</t>
+          <t>-57,83; 175,35</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,83</t>
+          <t>-1,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-61,9%</t>
+          <t>-17,43%</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 7,3</t>
+          <t>-13,43; 7,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 13,01</t>
+          <t>-4,19; 12,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 1,45</t>
+          <t>-10,54; 4,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-82,21; 193,34</t>
+          <t>-83,31; 207,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-92,75; 68,11</t>
+          <t>-82,04; 283,5</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,04</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-28,08%</t>
+          <t>-13,64%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 6,98</t>
+          <t>-3,3; 6,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 2,45</t>
+          <t>-7,32; 2,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,32</t>
+          <t>-3,64; 2,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 1,57</t>
+          <t>-6,47; 2,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 92,78</t>
+          <t>-30,46; 93,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,13</t>
+          <t>-100,0; 136,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-80,6; 119,34</t>
+          <t>-81,34; 125,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 20,11</t>
+          <t>-49,0; 30,55</t>
         </is>
       </c>
     </row>
